--- a/outputs/iteration-2/iteration-2-rtm-evidence.xlsx
+++ b/outputs/iteration-2/iteration-2-rtm-evidence.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R7f01017db19c4e74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R42316ede0ec24668"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ref83864c594d465d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R1ce68089021b4c1d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -840,7 +840,7 @@
         <x:v>Fail</x:v>
       </x:c>
       <x:c r="F12" s="19" t="str">
-        <x:v>BUG-001</x:v>
+        <x:v>UC-002-BUG-001</x:v>
       </x:c>
       <x:c r="G12" s="19" t="str">
         <x:v>TC-008R.png; console.json</x:v>
@@ -866,7 +866,7 @@
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="F13" s="20" t="str">
-        <x:v>BUG-001 blocker</x:v>
+        <x:v>UC-002-BUG-001 blocker</x:v>
       </x:c>
       <x:c r="G13" s="20" t="str">
         <x:v>TC-008R.png; console.json</x:v>
@@ -892,7 +892,7 @@
         <x:v>Fail</x:v>
       </x:c>
       <x:c r="F14" s="19" t="str">
-        <x:v>BUG-002</x:v>
+        <x:v>UC-003-BUG-001</x:v>
       </x:c>
       <x:c r="G14" s="19" t="str">
         <x:v>TC-005.png; TC-010.png</x:v>
@@ -918,7 +918,7 @@
         <x:v>Fail</x:v>
       </x:c>
       <x:c r="F15" s="20" t="str">
-        <x:v>BUG-002</x:v>
+        <x:v>UC-003-BUG-001</x:v>
       </x:c>
       <x:c r="G15" s="20" t="str">
         <x:v>TC-005.png; TC-011.png</x:v>
@@ -944,7 +944,7 @@
         <x:v>Fail</x:v>
       </x:c>
       <x:c r="F16" s="19" t="str">
-        <x:v>BUG-003</x:v>
+        <x:v>UC-003-BUG-002</x:v>
       </x:c>
       <x:c r="G16" s="19" t="str">
         <x:v>TC-012.png</x:v>
@@ -996,7 +996,7 @@
         <x:v>Fail</x:v>
       </x:c>
       <x:c r="F18" s="19" t="str">
-        <x:v>BUG-004</x:v>
+        <x:v>UC-002-BUG-002</x:v>
       </x:c>
       <x:c r="G18" s="19" t="str">
         <x:v>TC-014.png; TC-014-card-number-input.png; TC-014-expiry-input.png; TC-014-CVC-input.png</x:v>
@@ -1022,7 +1022,7 @@
         <x:v>Fail</x:v>
       </x:c>
       <x:c r="F19" s="20" t="str">
-        <x:v>BUG-006</x:v>
+        <x:v>UC-001-BUG-001</x:v>
       </x:c>
       <x:c r="G19" s="20" t="str">
         <x:v>TC-015-input.png; TC-015.png</x:v>
@@ -1048,7 +1048,7 @@
         <x:v>Fail</x:v>
       </x:c>
       <x:c r="F20" s="19" t="str">
-        <x:v>BUG-008</x:v>
+        <x:v>UC-004-BUG-001</x:v>
       </x:c>
       <x:c r="G20" s="19" t="str">
         <x:v>admin-smoke.json; TC-016-quotation.png</x:v>
@@ -1074,7 +1074,7 @@
         <x:v>Fail</x:v>
       </x:c>
       <x:c r="F21" s="20" t="str">
-        <x:v>BUG-009, scope to confirm</x:v>
+        <x:v>UC-004-SCOPE-001</x:v>
       </x:c>
       <x:c r="G21" s="20" t="str">
         <x:v>TC-017-filled.png</x:v>
@@ -1100,7 +1100,7 @@
         <x:v>Fail</x:v>
       </x:c>
       <x:c r="F22" s="19" t="str">
-        <x:v>BUG-007</x:v>
+        <x:v>SETUP-BUG-001</x:v>
       </x:c>
       <x:c r="G22" s="19" t="str">
         <x:v>clean-install.log; install-workaround.log</x:v>
